--- a/02_Metabarcoding/SummaryStat.xlsx
+++ b/02_Metabarcoding/SummaryStat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ushio/Work/Result/AllResult/2023_CeteDNApro/00_uCeta_Github/02_Metabarcoding/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ushio/Work/Result/AllResult/2023_CetaDNApro/00_uCeta_Github/02_Metabarcoding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA977D59-2242-7E46-81F8-4690E7DBFE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58672BE-0003-964B-BD2C-EFA047D1204B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="760" windowWidth="29420" windowHeight="18880" xr2:uid="{71903D1A-DD86-5547-8C2D-34A979C7017D}"/>
+    <workbookView xWindow="840" yWindow="760" windowWidth="29400" windowHeight="18880" xr2:uid="{71903D1A-DD86-5547-8C2D-34A979C7017D}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary stat" sheetId="7" r:id="rId1"/>
@@ -380,9 +380,6 @@
     <t>R023</t>
   </si>
   <si>
-    <t>Pool + HK water pilot samples</t>
-  </si>
-  <si>
     <t>Platform</t>
   </si>
   <si>
@@ -437,9 +434,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>Mu31F/Dc320R</t>
-  </si>
-  <si>
     <t>Dc671F/Dc1015R</t>
   </si>
   <si>
@@ -447,6 +441,12 @@
   </si>
   <si>
     <t>Mu9459F/Mu9822R</t>
+  </si>
+  <si>
+    <t>Pool + preliminary HK water samples</t>
+  </si>
+  <si>
+    <t>Mu31F/Dc320R (µCeta)</t>
   </si>
 </sst>
 </file>
@@ -557,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -607,6 +607,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -953,41 +962,41 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="23"/>
       <c r="B1" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>114</v>
-      </c>
       <c r="C2" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>125</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1006,7 +1015,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B5" s="26">
         <v>0.92079999999999995</v>
@@ -1026,7 +1035,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="21">
         <v>2572852</v>
@@ -1040,7 +1049,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="26">
         <v>0.77207873075318767</v>
@@ -1058,18 +1067,18 @@
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>127</v>
+    <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1080,32 +1089,32 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="22"/>
       <c r="B13" s="20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" s="20"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="22"/>
       <c r="B14" s="20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -1113,7 +1122,7 @@
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
       <c r="B15" s="27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="27"/>
